--- a/107男生宿舍名单.xlsx
+++ b/107男生宿舍名单.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\infomation-of-107\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\infomation-of-107\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="59">
   <si>
     <t>107班主任纪亚东
 17611228667</t>
@@ -70,96 +70,54 @@
     <t>男</t>
   </si>
   <si>
-    <t>13939386005</t>
-  </si>
-  <si>
     <t>走读</t>
   </si>
   <si>
     <t>崔佳乐</t>
   </si>
   <si>
-    <t>13525282268</t>
-  </si>
-  <si>
     <t>付泽熙</t>
   </si>
   <si>
-    <t>18239357168</t>
-  </si>
-  <si>
     <t>刘宇腾</t>
   </si>
   <si>
-    <t>18939343366</t>
-  </si>
-  <si>
     <t>李凯旋</t>
   </si>
   <si>
-    <t>15936777061</t>
-  </si>
-  <si>
     <t>张游龙</t>
   </si>
   <si>
-    <t>13461623165</t>
-  </si>
-  <si>
     <t>许钊迪</t>
   </si>
   <si>
-    <t>17339325202</t>
-  </si>
-  <si>
     <t>田啸童</t>
   </si>
   <si>
-    <t>13781357190</t>
-  </si>
-  <si>
     <t>5-5-1503</t>
   </si>
   <si>
     <t>房建设</t>
   </si>
   <si>
-    <t>13938339608</t>
-  </si>
-  <si>
     <t>孟宪爽</t>
   </si>
   <si>
     <t>刘珈宁</t>
   </si>
   <si>
-    <t>18303932266</t>
-  </si>
-  <si>
     <t>王梓航</t>
   </si>
   <si>
-    <t>15210263209</t>
-  </si>
-  <si>
     <t>宋世豪</t>
   </si>
   <si>
-    <t>13839279109</t>
-  </si>
-  <si>
     <t>李佳睿</t>
   </si>
   <si>
-    <t>18338020888</t>
-  </si>
-  <si>
     <t>王梓豪</t>
   </si>
   <si>
-    <t>18300650709</t>
-  </si>
-  <si>
     <t>刘家硕</t>
   </si>
   <si>
@@ -169,169 +127,91 @@
     <t>龙浩宇</t>
   </si>
   <si>
-    <t>13781379430</t>
-  </si>
-  <si>
     <t>王光辉</t>
   </si>
   <si>
-    <t>15039382562</t>
-  </si>
-  <si>
     <t>刘修阔</t>
   </si>
   <si>
-    <t>13523933662</t>
-  </si>
-  <si>
     <t>高一品</t>
   </si>
   <si>
-    <t>18739381405</t>
-  </si>
-  <si>
     <t>吴浩然</t>
   </si>
   <si>
-    <t>15939318302</t>
-  </si>
-  <si>
     <t>左晓阳</t>
   </si>
   <si>
     <t>李旭晨</t>
   </si>
   <si>
-    <t>13903935797</t>
-  </si>
-  <si>
     <t>白宇皓</t>
   </si>
   <si>
-    <t>15090218009</t>
-  </si>
-  <si>
     <t>5-5-1510</t>
   </si>
   <si>
     <t>李泽瑞</t>
   </si>
   <si>
-    <t>13623932898</t>
-  </si>
-  <si>
     <t>汪士航</t>
   </si>
   <si>
-    <t>15539339658</t>
-  </si>
-  <si>
     <t>冯梦乐</t>
   </si>
   <si>
-    <t>13193572112</t>
-  </si>
-  <si>
     <t>张献雷</t>
   </si>
   <si>
-    <t>15518512212</t>
-  </si>
-  <si>
     <t>崔一尚</t>
   </si>
   <si>
-    <t>13513943021</t>
-  </si>
-  <si>
     <t>杜晨阳</t>
   </si>
   <si>
-    <t>13839283759</t>
-  </si>
-  <si>
     <t>祁瀚辉</t>
   </si>
   <si>
-    <t>13781369836</t>
-  </si>
-  <si>
     <t>翟光辉</t>
   </si>
   <si>
-    <t>18238327212</t>
-  </si>
-  <si>
     <t>5-5-1508</t>
   </si>
   <si>
     <t>赵辰逸</t>
   </si>
   <si>
-    <t>18539330756</t>
-  </si>
-  <si>
     <t>关子豪</t>
   </si>
   <si>
-    <t>15839358163</t>
-  </si>
-  <si>
     <t>许敬涛</t>
   </si>
   <si>
-    <t>15518522809</t>
-  </si>
-  <si>
     <t>范明信</t>
   </si>
   <si>
-    <t>15890496073</t>
-  </si>
-  <si>
     <t>李名洋</t>
   </si>
   <si>
-    <t>15639306288</t>
-  </si>
-  <si>
     <t>孟伟旭</t>
   </si>
   <si>
-    <t>17339303182</t>
-  </si>
-  <si>
     <t>吴延旭</t>
   </si>
   <si>
-    <t>15936786198</t>
-  </si>
-  <si>
     <t>张跃虎</t>
   </si>
   <si>
-    <t>13643938925</t>
-  </si>
-  <si>
     <t>5-5-1506</t>
   </si>
   <si>
     <t>黄哲</t>
   </si>
   <si>
-    <t>18639352711</t>
-  </si>
-  <si>
     <t>赵腾源</t>
   </si>
   <si>
-    <t>13613932000</t>
-  </si>
-  <si>
     <t>刘鹏</t>
-  </si>
-  <si>
-    <t>18639372028</t>
   </si>
 </sst>
 </file>
@@ -344,7 +224,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -358,27 +238,10 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="黑体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="10.5"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color indexed="8"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="major"/>
     </font>
     <font>
       <u/>
@@ -719,27 +582,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="9">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -860,137 +708,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1003,29 +851,17 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1079,17 +915,7 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1390,13 +1216,13 @@
       <c r="D2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="4" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1407,20 +1233,20 @@
       <c r="B3" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="7" t="s">
-        <v>11</v>
+      <c r="E3" s="6">
+        <v>13939386005</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
       <c r="G3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1430,14 +1256,14 @@
       <c r="B4" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>13</v>
+      <c r="C4" s="5" t="s">
+        <v>12</v>
       </c>
       <c r="D4" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="7" t="s">
-        <v>14</v>
+      <c r="E4" s="6">
+        <v>13525282268</v>
       </c>
       <c r="F4">
         <v>2</v>
@@ -1450,20 +1276,20 @@
       <c r="B5" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>15</v>
+      <c r="C5" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="D5" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="7" t="s">
-        <v>16</v>
+      <c r="E5" s="6">
+        <v>18239357168</v>
       </c>
       <c r="F5">
         <v>3</v>
       </c>
       <c r="G5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1473,14 +1299,14 @@
       <c r="B6" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>17</v>
+      <c r="C6" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="D6" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="7" t="s">
-        <v>18</v>
+      <c r="E6" s="6">
+        <v>18939343366</v>
       </c>
       <c r="F6">
         <v>4</v>
@@ -1493,20 +1319,20 @@
       <c r="B7" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="6" t="s">
-        <v>19</v>
+      <c r="C7" s="5" t="s">
+        <v>15</v>
       </c>
       <c r="D7" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="7" t="s">
-        <v>20</v>
+      <c r="E7" s="6">
+        <v>15936777061</v>
       </c>
       <c r="F7">
         <v>5</v>
       </c>
       <c r="G7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1516,14 +1342,14 @@
       <c r="B8" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>21</v>
+      <c r="C8" s="5" t="s">
+        <v>16</v>
       </c>
       <c r="D8" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="7" t="s">
-        <v>22</v>
+      <c r="E8" s="6">
+        <v>13461623165</v>
       </c>
       <c r="F8">
         <v>6</v>
@@ -1536,14 +1362,14 @@
       <c r="B9" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>23</v>
+      <c r="C9" s="5" t="s">
+        <v>17</v>
       </c>
       <c r="D9" t="s">
         <v>10</v>
       </c>
-      <c r="E9" s="8" t="s">
-        <v>24</v>
+      <c r="E9" s="6">
+        <v>17339325202</v>
       </c>
       <c r="F9">
         <v>7</v>
@@ -1556,14 +1382,14 @@
       <c r="B10" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="6" t="s">
-        <v>25</v>
+      <c r="C10" s="5" t="s">
+        <v>18</v>
       </c>
       <c r="D10" t="s">
         <v>10</v>
       </c>
-      <c r="E10" s="7" t="s">
-        <v>26</v>
+      <c r="E10" s="6">
+        <v>13781357190</v>
       </c>
       <c r="F10">
         <v>8</v>
@@ -1574,22 +1400,22 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D11" t="s">
         <v>10</v>
       </c>
-      <c r="E11" s="7" t="s">
-        <v>29</v>
+      <c r="E11" s="6">
+        <v>13938339608</v>
       </c>
       <c r="F11">
         <v>1</v>
       </c>
       <c r="G11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -1597,15 +1423,15 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C12" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="D12" t="s">
         <v>10</v>
       </c>
-      <c r="E12" s="9">
+      <c r="E12" s="2">
         <v>13939312589</v>
       </c>
       <c r="F12">
@@ -1617,22 +1443,22 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C13" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="D13" t="s">
         <v>10</v>
       </c>
-      <c r="E13" s="7" t="s">
-        <v>32</v>
+      <c r="E13" s="6">
+        <v>18303932266</v>
       </c>
       <c r="F13">
         <v>3</v>
       </c>
       <c r="G13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -1640,16 +1466,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>33</v>
+        <v>19</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="D14" t="s">
         <v>10</v>
       </c>
-      <c r="E14" s="7" t="s">
-        <v>34</v>
+      <c r="E14" s="6">
+        <v>15210263209</v>
       </c>
       <c r="F14">
         <v>4</v>
@@ -1660,22 +1486,22 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>27</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>35</v>
+        <v>19</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>24</v>
       </c>
       <c r="D15" t="s">
         <v>10</v>
       </c>
-      <c r="E15" s="7" t="s">
-        <v>36</v>
+      <c r="E15" s="6">
+        <v>13839279109</v>
       </c>
       <c r="F15">
         <v>5</v>
       </c>
       <c r="G15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -1683,22 +1509,22 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C16" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="D16" t="s">
         <v>10</v>
       </c>
-      <c r="E16" s="7" t="s">
-        <v>38</v>
+      <c r="E16" s="6">
+        <v>18338020888</v>
       </c>
       <c r="F16">
         <v>6</v>
       </c>
       <c r="G16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1706,22 +1532,22 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C17" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="D17" t="s">
         <v>10</v>
       </c>
-      <c r="E17" s="7" t="s">
-        <v>40</v>
+      <c r="E17" s="6">
+        <v>18300650709</v>
       </c>
       <c r="F17">
         <v>7</v>
       </c>
       <c r="G17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1729,22 +1555,22 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" t="s">
         <v>27</v>
       </c>
-      <c r="C18" t="s">
-        <v>41</v>
-      </c>
       <c r="D18" t="s">
         <v>10</v>
       </c>
-      <c r="E18" s="9">
+      <c r="E18" s="2">
         <v>13839281869</v>
       </c>
       <c r="F18">
         <v>8</v>
       </c>
       <c r="G18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1752,22 +1578,22 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>42</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>43</v>
+        <v>28</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="D19" t="s">
         <v>10</v>
       </c>
-      <c r="E19" s="7" t="s">
-        <v>44</v>
+      <c r="E19" s="6">
+        <v>13781379430</v>
       </c>
       <c r="F19">
         <v>1</v>
       </c>
       <c r="G19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1775,16 +1601,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>42</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>45</v>
+        <v>28</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="D20" t="s">
         <v>10</v>
       </c>
-      <c r="E20" s="7" t="s">
-        <v>46</v>
+      <c r="E20" s="6">
+        <v>15039382562</v>
       </c>
       <c r="F20">
         <v>2</v>
@@ -1795,22 +1621,22 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>42</v>
-      </c>
-      <c r="C21" s="11" t="s">
-        <v>47</v>
+        <v>28</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="D21" t="s">
         <v>10</v>
       </c>
-      <c r="E21" s="7" t="s">
-        <v>48</v>
+      <c r="E21" s="6">
+        <v>13523933662</v>
       </c>
       <c r="F21">
         <v>3</v>
       </c>
       <c r="G21" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1818,16 +1644,16 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>42</v>
-      </c>
-      <c r="C22" s="11" t="s">
-        <v>49</v>
+        <v>28</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>32</v>
       </c>
       <c r="D22" t="s">
         <v>10</v>
       </c>
-      <c r="E22" s="7" t="s">
-        <v>50</v>
+      <c r="E22" s="6">
+        <v>18739381405</v>
       </c>
       <c r="F22">
         <v>4</v>
@@ -1838,22 +1664,22 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>42</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>51</v>
+        <v>28</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>33</v>
       </c>
       <c r="D23" t="s">
         <v>10</v>
       </c>
-      <c r="E23" s="7" t="s">
-        <v>52</v>
+      <c r="E23" s="6">
+        <v>15939318302</v>
       </c>
       <c r="F23">
         <v>5</v>
       </c>
       <c r="G23" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1861,15 +1687,15 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>42</v>
-      </c>
-      <c r="C24" s="11" t="s">
-        <v>53</v>
+        <v>28</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>34</v>
       </c>
       <c r="D24" t="s">
         <v>10</v>
       </c>
-      <c r="E24" s="7">
+      <c r="E24" s="2">
         <v>13721726762</v>
       </c>
       <c r="F24">
@@ -1881,22 +1707,22 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>42</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>54</v>
+        <v>28</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="D25" t="s">
         <v>10</v>
       </c>
-      <c r="E25" s="7" t="s">
-        <v>55</v>
+      <c r="E25" s="6">
+        <v>13903935797</v>
       </c>
       <c r="F25">
         <v>7</v>
       </c>
       <c r="G25" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1904,16 +1730,16 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>42</v>
-      </c>
-      <c r="C26" s="11" t="s">
-        <v>56</v>
+        <v>28</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>36</v>
       </c>
       <c r="D26" t="s">
         <v>10</v>
       </c>
-      <c r="E26" s="7" t="s">
-        <v>57</v>
+      <c r="E26" s="6">
+        <v>15090218009</v>
       </c>
       <c r="F26">
         <v>8</v>
@@ -1924,22 +1750,22 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>58</v>
-      </c>
-      <c r="C27" s="11" t="s">
-        <v>59</v>
+        <v>37</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>38</v>
       </c>
       <c r="D27" t="s">
         <v>10</v>
       </c>
-      <c r="E27" s="7" t="s">
-        <v>60</v>
+      <c r="E27" s="6">
+        <v>13623932898</v>
       </c>
       <c r="F27">
         <v>1</v>
       </c>
       <c r="G27" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1947,16 +1773,16 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>58</v>
-      </c>
-      <c r="C28" s="11" t="s">
-        <v>61</v>
+        <v>37</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>39</v>
       </c>
       <c r="D28" t="s">
         <v>10</v>
       </c>
-      <c r="E28" s="7" t="s">
-        <v>62</v>
+      <c r="E28" s="6">
+        <v>15539339658</v>
       </c>
       <c r="F28">
         <v>2</v>
@@ -1967,22 +1793,22 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>58</v>
-      </c>
-      <c r="C29" s="11" t="s">
-        <v>63</v>
+        <v>37</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>40</v>
       </c>
       <c r="D29" t="s">
         <v>10</v>
       </c>
-      <c r="E29" s="7" t="s">
-        <v>64</v>
+      <c r="E29" s="6">
+        <v>13193572112</v>
       </c>
       <c r="F29">
         <v>3</v>
       </c>
       <c r="G29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1990,16 +1816,16 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>58</v>
-      </c>
-      <c r="C30" s="11" t="s">
-        <v>65</v>
+        <v>37</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>41</v>
       </c>
       <c r="D30" t="s">
         <v>10</v>
       </c>
-      <c r="E30" s="7" t="s">
-        <v>66</v>
+      <c r="E30" s="6">
+        <v>15518512212</v>
       </c>
       <c r="F30">
         <v>4</v>
@@ -2010,22 +1836,22 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>58</v>
-      </c>
-      <c r="C31" s="11" t="s">
-        <v>67</v>
+        <v>37</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>42</v>
       </c>
       <c r="D31" t="s">
         <v>10</v>
       </c>
-      <c r="E31" s="7" t="s">
-        <v>68</v>
+      <c r="E31" s="6">
+        <v>13513943021</v>
       </c>
       <c r="F31">
         <v>5</v>
       </c>
       <c r="G31" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2033,16 +1859,16 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>58</v>
-      </c>
-      <c r="C32" s="11" t="s">
-        <v>69</v>
+        <v>37</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="D32" t="s">
         <v>10</v>
       </c>
-      <c r="E32" s="7" t="s">
-        <v>70</v>
+      <c r="E32" s="6">
+        <v>13839283759</v>
       </c>
       <c r="F32">
         <v>6</v>
@@ -2053,22 +1879,22 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>58</v>
-      </c>
-      <c r="C33" s="11" t="s">
-        <v>71</v>
+        <v>37</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>44</v>
       </c>
       <c r="D33" t="s">
         <v>10</v>
       </c>
-      <c r="E33" s="7" t="s">
-        <v>72</v>
+      <c r="E33" s="6">
+        <v>13781369836</v>
       </c>
       <c r="F33">
         <v>7</v>
       </c>
       <c r="G33" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2076,16 +1902,16 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>58</v>
-      </c>
-      <c r="C34" s="11" t="s">
-        <v>73</v>
+        <v>37</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>45</v>
       </c>
       <c r="D34" t="s">
         <v>10</v>
       </c>
-      <c r="E34" s="7" t="s">
-        <v>74</v>
+      <c r="E34" s="6">
+        <v>18238327212</v>
       </c>
       <c r="F34">
         <v>8</v>
@@ -2096,16 +1922,16 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>75</v>
-      </c>
-      <c r="C35" s="11" t="s">
-        <v>76</v>
+        <v>46</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>47</v>
       </c>
       <c r="D35" t="s">
         <v>10</v>
       </c>
-      <c r="E35" s="7" t="s">
-        <v>77</v>
+      <c r="E35" s="6">
+        <v>18539330756</v>
       </c>
       <c r="F35">
         <v>1</v>
@@ -2116,16 +1942,16 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>75</v>
-      </c>
-      <c r="C36" s="11" t="s">
-        <v>78</v>
+        <v>46</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>48</v>
       </c>
       <c r="D36" t="s">
         <v>10</v>
       </c>
-      <c r="E36" s="7" t="s">
-        <v>79</v>
+      <c r="E36" s="6">
+        <v>15839358163</v>
       </c>
       <c r="F36">
         <v>2</v>
@@ -2136,22 +1962,22 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>75</v>
-      </c>
-      <c r="C37" s="11" t="s">
-        <v>80</v>
+        <v>46</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>49</v>
       </c>
       <c r="D37" t="s">
         <v>10</v>
       </c>
-      <c r="E37" s="7" t="s">
-        <v>81</v>
+      <c r="E37" s="6">
+        <v>15518522809</v>
       </c>
       <c r="F37">
         <v>3</v>
       </c>
       <c r="G37" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2159,16 +1985,16 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>75</v>
-      </c>
-      <c r="C38" s="11" t="s">
-        <v>82</v>
+        <v>46</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>50</v>
       </c>
       <c r="D38" t="s">
         <v>10</v>
       </c>
-      <c r="E38" s="7" t="s">
-        <v>83</v>
+      <c r="E38" s="6">
+        <v>15890496073</v>
       </c>
       <c r="F38">
         <v>4</v>
@@ -2179,22 +2005,22 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>75</v>
-      </c>
-      <c r="C39" s="11" t="s">
-        <v>84</v>
+        <v>46</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>51</v>
       </c>
       <c r="D39" t="s">
         <v>10</v>
       </c>
-      <c r="E39" s="7" t="s">
-        <v>85</v>
+      <c r="E39" s="6">
+        <v>15639306288</v>
       </c>
       <c r="F39">
         <v>5</v>
       </c>
       <c r="G39" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2202,16 +2028,16 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>75</v>
-      </c>
-      <c r="C40" s="11" t="s">
-        <v>86</v>
+        <v>46</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>52</v>
       </c>
       <c r="D40" t="s">
         <v>10</v>
       </c>
-      <c r="E40" s="7" t="s">
-        <v>87</v>
+      <c r="E40" s="6">
+        <v>17339303182</v>
       </c>
       <c r="F40">
         <v>6</v>
@@ -2222,22 +2048,22 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>75</v>
-      </c>
-      <c r="C41" s="11" t="s">
-        <v>88</v>
+        <v>46</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>53</v>
       </c>
       <c r="D41" t="s">
         <v>10</v>
       </c>
-      <c r="E41" s="7" t="s">
-        <v>89</v>
+      <c r="E41" s="6">
+        <v>15936786198</v>
       </c>
       <c r="F41">
         <v>7</v>
       </c>
       <c r="G41" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2245,16 +2071,16 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>75</v>
-      </c>
-      <c r="C42" s="11" t="s">
-        <v>90</v>
+        <v>46</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>54</v>
       </c>
       <c r="D42" t="s">
         <v>10</v>
       </c>
-      <c r="E42" s="7" t="s">
-        <v>91</v>
+      <c r="E42" s="6">
+        <v>13643938925</v>
       </c>
       <c r="F42">
         <v>8</v>
@@ -2265,22 +2091,22 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>92</v>
-      </c>
-      <c r="C43" s="10" t="s">
-        <v>93</v>
+        <v>55</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>56</v>
       </c>
       <c r="D43" t="s">
         <v>10</v>
       </c>
-      <c r="E43" s="7" t="s">
-        <v>94</v>
+      <c r="E43" s="6">
+        <v>18639352711</v>
       </c>
       <c r="F43">
         <v>1</v>
       </c>
       <c r="G43" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -2288,22 +2114,22 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>92</v>
-      </c>
-      <c r="C44" s="11" t="s">
-        <v>95</v>
+        <v>55</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>57</v>
       </c>
       <c r="D44" t="s">
         <v>10</v>
       </c>
-      <c r="E44" s="7" t="s">
-        <v>96</v>
+      <c r="E44" s="6">
+        <v>13613932000</v>
       </c>
       <c r="F44">
         <v>3</v>
       </c>
       <c r="G44" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -2311,22 +2137,22 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>92</v>
+        <v>55</v>
       </c>
       <c r="C45" t="s">
-        <v>97</v>
+        <v>58</v>
       </c>
       <c r="D45" t="s">
         <v>10</v>
       </c>
-      <c r="E45" s="7" t="s">
-        <v>98</v>
+      <c r="E45" s="6">
+        <v>18639372028</v>
       </c>
       <c r="F45">
         <v>5</v>
       </c>
       <c r="G45" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -2340,13 +2166,8 @@
     <cfRule type="duplicateValues" dxfId="0" priority="9"/>
     <cfRule type="duplicateValues" dxfId="0" priority="15"/>
     <cfRule type="duplicateValues" dxfId="0" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="21"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E3 E4:E6 E7 E8:E11 E12:E13 E14 E15 E16:E18 E19:E24 E25 E26 E27:E29 E30 E31:E33 E34:E35 E36:E37 E38:E39 E40:E45">
-    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="21"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/107男生宿舍名单.xlsx
+++ b/107男生宿舍名单.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="59">
   <si>
     <t>107班主任纪亚东
 17611228667</t>
@@ -70,96 +70,54 @@
     <t>男</t>
   </si>
   <si>
-    <t>13939386005</t>
-  </si>
-  <si>
     <t>走读</t>
   </si>
   <si>
     <t>崔佳乐</t>
   </si>
   <si>
-    <t>13525282268</t>
-  </si>
-  <si>
     <t>付泽熙</t>
   </si>
   <si>
-    <t>18239357168</t>
-  </si>
-  <si>
     <t>刘宇腾</t>
   </si>
   <si>
-    <t>18939343366</t>
-  </si>
-  <si>
     <t>李凯旋</t>
   </si>
   <si>
-    <t>15936777061</t>
-  </si>
-  <si>
     <t>张游龙</t>
   </si>
   <si>
-    <t>13461623165</t>
-  </si>
-  <si>
     <t>许钊迪</t>
   </si>
   <si>
-    <t>17339325202</t>
-  </si>
-  <si>
     <t>田啸童</t>
   </si>
   <si>
-    <t>13781357190</t>
-  </si>
-  <si>
     <t>5-5-1503</t>
   </si>
   <si>
     <t>房建设</t>
   </si>
   <si>
-    <t>13938339608</t>
-  </si>
-  <si>
     <t>孟宪爽</t>
   </si>
   <si>
     <t>刘珈宁</t>
   </si>
   <si>
-    <t>18303932266</t>
-  </si>
-  <si>
     <t>王梓航</t>
   </si>
   <si>
-    <t>15210263209</t>
-  </si>
-  <si>
     <t>宋世豪</t>
   </si>
   <si>
-    <t>13839279109</t>
-  </si>
-  <si>
     <t>李佳睿</t>
   </si>
   <si>
-    <t>18338020888</t>
-  </si>
-  <si>
     <t>王梓豪</t>
   </si>
   <si>
-    <t>18300650709</t>
-  </si>
-  <si>
     <t>刘家硕</t>
   </si>
   <si>
@@ -169,169 +127,91 @@
     <t>龙浩宇</t>
   </si>
   <si>
-    <t>13781379430</t>
-  </si>
-  <si>
     <t>王光辉</t>
   </si>
   <si>
-    <t>15039382562</t>
-  </si>
-  <si>
     <t>刘修阔</t>
   </si>
   <si>
-    <t>13523933662</t>
-  </si>
-  <si>
     <t>高一品</t>
   </si>
   <si>
-    <t>18739381405</t>
-  </si>
-  <si>
     <t>吴浩然</t>
   </si>
   <si>
-    <t>15939318302</t>
-  </si>
-  <si>
     <t>左晓阳</t>
   </si>
   <si>
     <t>李旭晨</t>
   </si>
   <si>
-    <t>13903935797</t>
-  </si>
-  <si>
     <t>白宇皓</t>
   </si>
   <si>
-    <t>15090218009</t>
-  </si>
-  <si>
     <t>5-5-1510</t>
   </si>
   <si>
     <t>李泽瑞</t>
   </si>
   <si>
-    <t>13623932898</t>
-  </si>
-  <si>
     <t>汪士航</t>
   </si>
   <si>
-    <t>15539339658</t>
-  </si>
-  <si>
     <t>冯梦乐</t>
   </si>
   <si>
-    <t>13193572112</t>
-  </si>
-  <si>
     <t>张献雷</t>
   </si>
   <si>
-    <t>15518512212</t>
-  </si>
-  <si>
     <t>崔一尚</t>
   </si>
   <si>
-    <t>13513943021</t>
-  </si>
-  <si>
     <t>杜晨阳</t>
   </si>
   <si>
-    <t>13839283759</t>
-  </si>
-  <si>
     <t>祁瀚辉</t>
   </si>
   <si>
-    <t>13781369836</t>
-  </si>
-  <si>
     <t>翟光辉</t>
   </si>
   <si>
-    <t>18238327212</t>
-  </si>
-  <si>
     <t>5-5-1508</t>
   </si>
   <si>
     <t>赵辰逸</t>
   </si>
   <si>
-    <t>18539330756</t>
-  </si>
-  <si>
     <t>关子豪</t>
   </si>
   <si>
-    <t>15839358163</t>
-  </si>
-  <si>
     <t>许敬涛</t>
   </si>
   <si>
-    <t>15518522809</t>
-  </si>
-  <si>
     <t>范明信</t>
   </si>
   <si>
-    <t>15890496073</t>
-  </si>
-  <si>
     <t>李名洋</t>
   </si>
   <si>
-    <t>15639306288</t>
-  </si>
-  <si>
     <t>孟伟旭</t>
   </si>
   <si>
-    <t>17339303182</t>
-  </si>
-  <si>
     <t>吴延旭</t>
   </si>
   <si>
-    <t>15936786198</t>
-  </si>
-  <si>
     <t>张跃虎</t>
   </si>
   <si>
-    <t>13643938925</t>
-  </si>
-  <si>
     <t>5-5-1506</t>
   </si>
   <si>
     <t>黄哲</t>
   </si>
   <si>
-    <t>18639352711</t>
-  </si>
-  <si>
     <t>赵腾源</t>
   </si>
   <si>
-    <t>13613932000</t>
-  </si>
-  <si>
     <t>刘鹏</t>
-  </si>
-  <si>
-    <t>18639372028</t>
   </si>
 </sst>
 </file>
@@ -344,41 +224,13 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="黑体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color indexed="8"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="major"/>
     </font>
     <font>
       <u/>
@@ -719,27 +571,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="9">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -860,171 +697,141 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1079,28 +886,6 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1367,36 +1152,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-    </row>
-    <row r="2" ht="14.25" spans="1:7">
-      <c r="A2" s="3" t="s">
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1407,20 +1186,20 @@
       <c r="B3" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" t="s">
         <v>9</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="7" t="s">
-        <v>11</v>
+      <c r="E3" s="1">
+        <v>13939386005</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
       <c r="G3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1430,14 +1209,14 @@
       <c r="B4" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>13</v>
+      <c r="C4" t="s">
+        <v>12</v>
       </c>
       <c r="D4" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="7" t="s">
-        <v>14</v>
+      <c r="E4" s="1">
+        <v>13525282268</v>
       </c>
       <c r="F4">
         <v>2</v>
@@ -1450,20 +1229,20 @@
       <c r="B5" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>15</v>
+      <c r="C5" t="s">
+        <v>13</v>
       </c>
       <c r="D5" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="7" t="s">
-        <v>16</v>
+      <c r="E5" s="1">
+        <v>18239357168</v>
       </c>
       <c r="F5">
         <v>3</v>
       </c>
       <c r="G5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1473,14 +1252,14 @@
       <c r="B6" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>17</v>
+      <c r="C6" t="s">
+        <v>14</v>
       </c>
       <c r="D6" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="7" t="s">
-        <v>18</v>
+      <c r="E6" s="1">
+        <v>18939343366</v>
       </c>
       <c r="F6">
         <v>4</v>
@@ -1493,20 +1272,20 @@
       <c r="B7" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="6" t="s">
-        <v>19</v>
+      <c r="C7" t="s">
+        <v>15</v>
       </c>
       <c r="D7" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="7" t="s">
-        <v>20</v>
+      <c r="E7" s="1">
+        <v>15936777061</v>
       </c>
       <c r="F7">
         <v>5</v>
       </c>
       <c r="G7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1516,14 +1295,14 @@
       <c r="B8" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>21</v>
+      <c r="C8" t="s">
+        <v>16</v>
       </c>
       <c r="D8" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="7" t="s">
-        <v>22</v>
+      <c r="E8" s="1">
+        <v>13461623165</v>
       </c>
       <c r="F8">
         <v>6</v>
@@ -1536,14 +1315,14 @@
       <c r="B9" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>23</v>
+      <c r="C9" t="s">
+        <v>17</v>
       </c>
       <c r="D9" t="s">
         <v>10</v>
       </c>
-      <c r="E9" s="8" t="s">
-        <v>24</v>
+      <c r="E9" s="1">
+        <v>17339325202</v>
       </c>
       <c r="F9">
         <v>7</v>
@@ -1556,14 +1335,14 @@
       <c r="B10" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="6" t="s">
-        <v>25</v>
+      <c r="C10" t="s">
+        <v>18</v>
       </c>
       <c r="D10" t="s">
         <v>10</v>
       </c>
-      <c r="E10" s="7" t="s">
-        <v>26</v>
+      <c r="E10" s="1">
+        <v>13781357190</v>
       </c>
       <c r="F10">
         <v>8</v>
@@ -1574,22 +1353,22 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D11" t="s">
         <v>10</v>
       </c>
-      <c r="E11" s="7" t="s">
-        <v>29</v>
+      <c r="E11" s="1">
+        <v>13938339608</v>
       </c>
       <c r="F11">
         <v>1</v>
       </c>
       <c r="G11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -1597,15 +1376,15 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C12" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="D12" t="s">
         <v>10</v>
       </c>
-      <c r="E12" s="9">
+      <c r="E12">
         <v>13939312589</v>
       </c>
       <c r="F12">
@@ -1617,22 +1396,22 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C13" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="D13" t="s">
         <v>10</v>
       </c>
-      <c r="E13" s="7" t="s">
-        <v>32</v>
+      <c r="E13" s="1">
+        <v>18303932266</v>
       </c>
       <c r="F13">
         <v>3</v>
       </c>
       <c r="G13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -1640,16 +1419,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>33</v>
+        <v>19</v>
+      </c>
+      <c r="C14" t="s">
+        <v>23</v>
       </c>
       <c r="D14" t="s">
         <v>10</v>
       </c>
-      <c r="E14" s="7" t="s">
-        <v>34</v>
+      <c r="E14" s="1">
+        <v>15210263209</v>
       </c>
       <c r="F14">
         <v>4</v>
@@ -1660,22 +1439,22 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>27</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>35</v>
+        <v>19</v>
+      </c>
+      <c r="C15" t="s">
+        <v>24</v>
       </c>
       <c r="D15" t="s">
         <v>10</v>
       </c>
-      <c r="E15" s="7" t="s">
-        <v>36</v>
+      <c r="E15" s="1">
+        <v>13839279109</v>
       </c>
       <c r="F15">
         <v>5</v>
       </c>
       <c r="G15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -1683,22 +1462,22 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C16" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="D16" t="s">
         <v>10</v>
       </c>
-      <c r="E16" s="7" t="s">
-        <v>38</v>
+      <c r="E16" s="1">
+        <v>18338020888</v>
       </c>
       <c r="F16">
         <v>6</v>
       </c>
       <c r="G16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1706,22 +1485,22 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C17" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="D17" t="s">
         <v>10</v>
       </c>
-      <c r="E17" s="7" t="s">
-        <v>40</v>
+      <c r="E17" s="1">
+        <v>18300650709</v>
       </c>
       <c r="F17">
         <v>7</v>
       </c>
       <c r="G17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1729,22 +1508,22 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" t="s">
         <v>27</v>
       </c>
-      <c r="C18" t="s">
-        <v>41</v>
-      </c>
       <c r="D18" t="s">
         <v>10</v>
       </c>
-      <c r="E18" s="9">
+      <c r="E18">
         <v>13839281869</v>
       </c>
       <c r="F18">
         <v>8</v>
       </c>
       <c r="G18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1752,22 +1531,22 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>42</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>43</v>
+        <v>28</v>
+      </c>
+      <c r="C19" t="s">
+        <v>29</v>
       </c>
       <c r="D19" t="s">
         <v>10</v>
       </c>
-      <c r="E19" s="7" t="s">
-        <v>44</v>
+      <c r="E19" s="1">
+        <v>13781379430</v>
       </c>
       <c r="F19">
         <v>1</v>
       </c>
       <c r="G19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1775,16 +1554,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>42</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>45</v>
+        <v>28</v>
+      </c>
+      <c r="C20" t="s">
+        <v>30</v>
       </c>
       <c r="D20" t="s">
         <v>10</v>
       </c>
-      <c r="E20" s="7" t="s">
-        <v>46</v>
+      <c r="E20" s="1">
+        <v>15039382562</v>
       </c>
       <c r="F20">
         <v>2</v>
@@ -1795,22 +1574,22 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>42</v>
-      </c>
-      <c r="C21" s="11" t="s">
-        <v>47</v>
+        <v>28</v>
+      </c>
+      <c r="C21" t="s">
+        <v>31</v>
       </c>
       <c r="D21" t="s">
         <v>10</v>
       </c>
-      <c r="E21" s="7" t="s">
-        <v>48</v>
+      <c r="E21" s="1">
+        <v>13523933662</v>
       </c>
       <c r="F21">
         <v>3</v>
       </c>
       <c r="G21" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1818,16 +1597,16 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>42</v>
-      </c>
-      <c r="C22" s="11" t="s">
-        <v>49</v>
+        <v>28</v>
+      </c>
+      <c r="C22" t="s">
+        <v>32</v>
       </c>
       <c r="D22" t="s">
         <v>10</v>
       </c>
-      <c r="E22" s="7" t="s">
-        <v>50</v>
+      <c r="E22" s="1">
+        <v>18739381405</v>
       </c>
       <c r="F22">
         <v>4</v>
@@ -1838,22 +1617,22 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>42</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>51</v>
+        <v>28</v>
+      </c>
+      <c r="C23" t="s">
+        <v>33</v>
       </c>
       <c r="D23" t="s">
         <v>10</v>
       </c>
-      <c r="E23" s="7" t="s">
-        <v>52</v>
+      <c r="E23" s="1">
+        <v>15939318302</v>
       </c>
       <c r="F23">
         <v>5</v>
       </c>
       <c r="G23" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1861,15 +1640,15 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>42</v>
-      </c>
-      <c r="C24" s="11" t="s">
-        <v>53</v>
+        <v>28</v>
+      </c>
+      <c r="C24" t="s">
+        <v>34</v>
       </c>
       <c r="D24" t="s">
         <v>10</v>
       </c>
-      <c r="E24" s="7">
+      <c r="E24">
         <v>13721726762</v>
       </c>
       <c r="F24">
@@ -1881,22 +1660,22 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>42</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>54</v>
+        <v>28</v>
+      </c>
+      <c r="C25" t="s">
+        <v>35</v>
       </c>
       <c r="D25" t="s">
         <v>10</v>
       </c>
-      <c r="E25" s="7" t="s">
-        <v>55</v>
+      <c r="E25" s="1">
+        <v>13903935797</v>
       </c>
       <c r="F25">
         <v>7</v>
       </c>
       <c r="G25" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1904,16 +1683,16 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>42</v>
-      </c>
-      <c r="C26" s="11" t="s">
-        <v>56</v>
+        <v>28</v>
+      </c>
+      <c r="C26" t="s">
+        <v>36</v>
       </c>
       <c r="D26" t="s">
         <v>10</v>
       </c>
-      <c r="E26" s="7" t="s">
-        <v>57</v>
+      <c r="E26" s="1">
+        <v>15090218009</v>
       </c>
       <c r="F26">
         <v>8</v>
@@ -1924,22 +1703,22 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>58</v>
-      </c>
-      <c r="C27" s="11" t="s">
-        <v>59</v>
+        <v>37</v>
+      </c>
+      <c r="C27" t="s">
+        <v>38</v>
       </c>
       <c r="D27" t="s">
         <v>10</v>
       </c>
-      <c r="E27" s="7" t="s">
-        <v>60</v>
+      <c r="E27" s="1">
+        <v>13623932898</v>
       </c>
       <c r="F27">
         <v>1</v>
       </c>
       <c r="G27" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1947,16 +1726,16 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>58</v>
-      </c>
-      <c r="C28" s="11" t="s">
-        <v>61</v>
+        <v>37</v>
+      </c>
+      <c r="C28" t="s">
+        <v>39</v>
       </c>
       <c r="D28" t="s">
         <v>10</v>
       </c>
-      <c r="E28" s="7" t="s">
-        <v>62</v>
+      <c r="E28" s="1">
+        <v>15539339658</v>
       </c>
       <c r="F28">
         <v>2</v>
@@ -1967,22 +1746,22 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>58</v>
-      </c>
-      <c r="C29" s="11" t="s">
-        <v>63</v>
+        <v>37</v>
+      </c>
+      <c r="C29" t="s">
+        <v>40</v>
       </c>
       <c r="D29" t="s">
         <v>10</v>
       </c>
-      <c r="E29" s="7" t="s">
-        <v>64</v>
+      <c r="E29" s="1">
+        <v>13193572112</v>
       </c>
       <c r="F29">
         <v>3</v>
       </c>
       <c r="G29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1990,16 +1769,16 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>58</v>
-      </c>
-      <c r="C30" s="11" t="s">
-        <v>65</v>
+        <v>37</v>
+      </c>
+      <c r="C30" t="s">
+        <v>41</v>
       </c>
       <c r="D30" t="s">
         <v>10</v>
       </c>
-      <c r="E30" s="7" t="s">
-        <v>66</v>
+      <c r="E30" s="1">
+        <v>15518512212</v>
       </c>
       <c r="F30">
         <v>4</v>
@@ -2010,22 +1789,22 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>58</v>
-      </c>
-      <c r="C31" s="11" t="s">
-        <v>67</v>
+        <v>37</v>
+      </c>
+      <c r="C31" t="s">
+        <v>42</v>
       </c>
       <c r="D31" t="s">
         <v>10</v>
       </c>
-      <c r="E31" s="7" t="s">
-        <v>68</v>
+      <c r="E31" s="1">
+        <v>13513943021</v>
       </c>
       <c r="F31">
         <v>5</v>
       </c>
       <c r="G31" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2033,16 +1812,16 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>58</v>
-      </c>
-      <c r="C32" s="11" t="s">
-        <v>69</v>
+        <v>37</v>
+      </c>
+      <c r="C32" t="s">
+        <v>43</v>
       </c>
       <c r="D32" t="s">
         <v>10</v>
       </c>
-      <c r="E32" s="7" t="s">
-        <v>70</v>
+      <c r="E32" s="1">
+        <v>13839283759</v>
       </c>
       <c r="F32">
         <v>6</v>
@@ -2053,22 +1832,22 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>58</v>
-      </c>
-      <c r="C33" s="11" t="s">
-        <v>71</v>
+        <v>37</v>
+      </c>
+      <c r="C33" t="s">
+        <v>44</v>
       </c>
       <c r="D33" t="s">
         <v>10</v>
       </c>
-      <c r="E33" s="7" t="s">
-        <v>72</v>
+      <c r="E33" s="1">
+        <v>13781369836</v>
       </c>
       <c r="F33">
         <v>7</v>
       </c>
       <c r="G33" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2076,16 +1855,16 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>58</v>
-      </c>
-      <c r="C34" s="11" t="s">
-        <v>73</v>
+        <v>37</v>
+      </c>
+      <c r="C34" t="s">
+        <v>45</v>
       </c>
       <c r="D34" t="s">
         <v>10</v>
       </c>
-      <c r="E34" s="7" t="s">
-        <v>74</v>
+      <c r="E34" s="1">
+        <v>18238327212</v>
       </c>
       <c r="F34">
         <v>8</v>
@@ -2096,16 +1875,16 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>75</v>
-      </c>
-      <c r="C35" s="11" t="s">
-        <v>76</v>
+        <v>46</v>
+      </c>
+      <c r="C35" t="s">
+        <v>47</v>
       </c>
       <c r="D35" t="s">
         <v>10</v>
       </c>
-      <c r="E35" s="7" t="s">
-        <v>77</v>
+      <c r="E35" s="1">
+        <v>18539330756</v>
       </c>
       <c r="F35">
         <v>1</v>
@@ -2116,16 +1895,16 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>75</v>
-      </c>
-      <c r="C36" s="11" t="s">
-        <v>78</v>
+        <v>46</v>
+      </c>
+      <c r="C36" t="s">
+        <v>48</v>
       </c>
       <c r="D36" t="s">
         <v>10</v>
       </c>
-      <c r="E36" s="7" t="s">
-        <v>79</v>
+      <c r="E36" s="1">
+        <v>15839358163</v>
       </c>
       <c r="F36">
         <v>2</v>
@@ -2136,22 +1915,22 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>75</v>
-      </c>
-      <c r="C37" s="11" t="s">
-        <v>80</v>
+        <v>46</v>
+      </c>
+      <c r="C37" t="s">
+        <v>49</v>
       </c>
       <c r="D37" t="s">
         <v>10</v>
       </c>
-      <c r="E37" s="7" t="s">
-        <v>81</v>
+      <c r="E37" s="1">
+        <v>15518522809</v>
       </c>
       <c r="F37">
         <v>3</v>
       </c>
       <c r="G37" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2159,16 +1938,16 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>75</v>
-      </c>
-      <c r="C38" s="11" t="s">
-        <v>82</v>
+        <v>46</v>
+      </c>
+      <c r="C38" t="s">
+        <v>50</v>
       </c>
       <c r="D38" t="s">
         <v>10</v>
       </c>
-      <c r="E38" s="7" t="s">
-        <v>83</v>
+      <c r="E38" s="1">
+        <v>15890496073</v>
       </c>
       <c r="F38">
         <v>4</v>
@@ -2179,22 +1958,22 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>75</v>
-      </c>
-      <c r="C39" s="11" t="s">
-        <v>84</v>
+        <v>46</v>
+      </c>
+      <c r="C39" t="s">
+        <v>51</v>
       </c>
       <c r="D39" t="s">
         <v>10</v>
       </c>
-      <c r="E39" s="7" t="s">
-        <v>85</v>
+      <c r="E39" s="1">
+        <v>15639306288</v>
       </c>
       <c r="F39">
         <v>5</v>
       </c>
       <c r="G39" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2202,16 +1981,16 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>75</v>
-      </c>
-      <c r="C40" s="11" t="s">
-        <v>86</v>
+        <v>46</v>
+      </c>
+      <c r="C40" t="s">
+        <v>52</v>
       </c>
       <c r="D40" t="s">
         <v>10</v>
       </c>
-      <c r="E40" s="7" t="s">
-        <v>87</v>
+      <c r="E40" s="1">
+        <v>17339303182</v>
       </c>
       <c r="F40">
         <v>6</v>
@@ -2222,22 +2001,22 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>75</v>
-      </c>
-      <c r="C41" s="11" t="s">
-        <v>88</v>
+        <v>46</v>
+      </c>
+      <c r="C41" t="s">
+        <v>53</v>
       </c>
       <c r="D41" t="s">
         <v>10</v>
       </c>
-      <c r="E41" s="7" t="s">
-        <v>89</v>
+      <c r="E41" s="1">
+        <v>15936786198</v>
       </c>
       <c r="F41">
         <v>7</v>
       </c>
       <c r="G41" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2245,16 +2024,16 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>75</v>
-      </c>
-      <c r="C42" s="11" t="s">
-        <v>90</v>
+        <v>46</v>
+      </c>
+      <c r="C42" t="s">
+        <v>54</v>
       </c>
       <c r="D42" t="s">
         <v>10</v>
       </c>
-      <c r="E42" s="7" t="s">
-        <v>91</v>
+      <c r="E42" s="1">
+        <v>13643938925</v>
       </c>
       <c r="F42">
         <v>8</v>
@@ -2265,22 +2044,22 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>92</v>
-      </c>
-      <c r="C43" s="10" t="s">
-        <v>93</v>
+        <v>55</v>
+      </c>
+      <c r="C43" t="s">
+        <v>56</v>
       </c>
       <c r="D43" t="s">
         <v>10</v>
       </c>
-      <c r="E43" s="7" t="s">
-        <v>94</v>
+      <c r="E43" s="1">
+        <v>18639352711</v>
       </c>
       <c r="F43">
         <v>1</v>
       </c>
       <c r="G43" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -2288,22 +2067,22 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>92</v>
-      </c>
-      <c r="C44" s="11" t="s">
-        <v>95</v>
+        <v>55</v>
+      </c>
+      <c r="C44" t="s">
+        <v>57</v>
       </c>
       <c r="D44" t="s">
         <v>10</v>
       </c>
-      <c r="E44" s="7" t="s">
-        <v>96</v>
+      <c r="E44" s="1">
+        <v>13613932000</v>
       </c>
       <c r="F44">
         <v>3</v>
       </c>
       <c r="G44" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -2311,43 +2090,28 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>92</v>
+        <v>55</v>
       </c>
       <c r="C45" t="s">
-        <v>97</v>
+        <v>58</v>
       </c>
       <c r="D45" t="s">
         <v>10</v>
       </c>
-      <c r="E45" s="7" t="s">
-        <v>98</v>
+      <c r="E45" s="1">
+        <v>18639372028</v>
       </c>
       <c r="F45">
         <v>5</v>
       </c>
       <c r="G45" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
   <sortState ref="A3:G45">
     <sortCondition ref="A3"/>
   </sortState>
-  <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <conditionalFormatting sqref="C3:C45">
-    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="21"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E3 E4:E6 E7 E8:E11 E12:E13 E14 E15 E16:E18 E19:E24 E25 E26 E27:E29 E30 E31:E33 E34:E35 E36:E37 E38:E39 E40:E45">
-    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>

--- a/107男生宿舍名单.xlsx
+++ b/107男生宿舍名单.xlsx
@@ -34,11 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="59">
-  <si>
-    <t>107班主任纪亚东
-17611228667</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="58">
   <si>
     <t>序号</t>
   </si>
@@ -58,7 +54,7 @@
     <t>床位号</t>
   </si>
   <si>
-    <t>是否走读</t>
+    <t>是否走读留铺</t>
   </si>
   <si>
     <t>5-5-1505</t>
@@ -70,7 +66,7 @@
     <t>男</t>
   </si>
   <si>
-    <t>走读</t>
+    <t>走读留铺</t>
   </si>
   <si>
     <t>崔佳乐</t>
@@ -1145,7 +1141,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="5" max="5" width="13.75" customWidth="1"/>
@@ -1155,957 +1151,952 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" t="s">
+      <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" t="s">
-        <v>6</v>
+        <v>9</v>
+      </c>
+      <c r="E2" s="1">
+        <v>13939386005</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
       </c>
       <c r="G2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E3" s="1">
-        <v>13939386005</v>
+        <v>13525282268</v>
       </c>
       <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
         <v>12</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E4" s="1">
-        <v>13525282268</v>
+        <v>18239357168</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="G4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C5" t="s">
         <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E5" s="1">
-        <v>18239357168</v>
+        <v>18939343366</v>
       </c>
       <c r="F5">
-        <v>3</v>
-      </c>
-      <c r="G5" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C6" t="s">
         <v>14</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E6" s="1">
-        <v>18939343366</v>
+        <v>15936777061</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="G6" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C7" t="s">
         <v>15</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E7" s="1">
-        <v>15936777061</v>
+        <v>13461623165</v>
       </c>
       <c r="F7">
-        <v>5</v>
-      </c>
-      <c r="G7" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C8" t="s">
         <v>16</v>
       </c>
       <c r="D8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E8" s="1">
-        <v>13461623165</v>
+        <v>17339325202</v>
       </c>
       <c r="F8">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
         <v>7</v>
-      </c>
-      <c r="B9" t="s">
-        <v>8</v>
       </c>
       <c r="C9" t="s">
         <v>17</v>
       </c>
       <c r="D9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E9" s="1">
-        <v>17339325202</v>
+        <v>13781357190</v>
       </c>
       <c r="F9">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E10" s="1">
-        <v>13781357190</v>
+        <v>13938339608</v>
       </c>
       <c r="F10">
-        <v>8</v>
+        <v>1</v>
+      </c>
+      <c r="G10" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C11" t="s">
         <v>20</v>
       </c>
       <c r="D11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" s="1">
-        <v>13938339608</v>
+        <v>9</v>
+      </c>
+      <c r="E11">
+        <v>13939312589</v>
       </c>
       <c r="F11">
-        <v>1</v>
-      </c>
-      <c r="G11" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C12" t="s">
         <v>21</v>
       </c>
       <c r="D12" t="s">
-        <v>10</v>
-      </c>
-      <c r="E12">
-        <v>13939312589</v>
+        <v>9</v>
+      </c>
+      <c r="E12" s="1">
+        <v>18303932266</v>
       </c>
       <c r="F12">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="G12" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C13" t="s">
         <v>22</v>
       </c>
       <c r="D13" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E13" s="1">
-        <v>18303932266</v>
+        <v>15210263209</v>
       </c>
       <c r="F13">
-        <v>3</v>
-      </c>
-      <c r="G13" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C14" t="s">
         <v>23</v>
       </c>
       <c r="D14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E14" s="1">
-        <v>15210263209</v>
+        <v>13839279109</v>
       </c>
       <c r="F14">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="G14" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C15" t="s">
         <v>24</v>
       </c>
       <c r="D15" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E15" s="1">
-        <v>13839279109</v>
+        <v>18338020888</v>
       </c>
       <c r="F15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C16" t="s">
         <v>25</v>
       </c>
       <c r="D16" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E16" s="1">
-        <v>18338020888</v>
+        <v>18300650709</v>
       </c>
       <c r="F16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G16" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C17" t="s">
         <v>26</v>
       </c>
       <c r="D17" t="s">
-        <v>10</v>
-      </c>
-      <c r="E17" s="1">
-        <v>18300650709</v>
+        <v>9</v>
+      </c>
+      <c r="E17">
+        <v>13839281869</v>
       </c>
       <c r="F17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G17" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="C18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E18">
-        <v>13839281869</v>
+        <v>9</v>
+      </c>
+      <c r="E18" s="1">
+        <v>13781379430</v>
       </c>
       <c r="F18">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C19" t="s">
         <v>29</v>
       </c>
       <c r="D19" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E19" s="1">
-        <v>13781379430</v>
+        <v>15039382562</v>
       </c>
       <c r="F19">
-        <v>1</v>
-      </c>
-      <c r="G19" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C20" t="s">
         <v>30</v>
       </c>
       <c r="D20" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E20" s="1">
-        <v>15039382562</v>
+        <v>13523933662</v>
       </c>
       <c r="F20">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="G20" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C21" t="s">
         <v>31</v>
       </c>
       <c r="D21" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E21" s="1">
-        <v>13523933662</v>
+        <v>18739381405</v>
       </c>
       <c r="F21">
-        <v>3</v>
-      </c>
-      <c r="G21" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C22" t="s">
         <v>32</v>
       </c>
       <c r="D22" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E22" s="1">
-        <v>18739381405</v>
+        <v>15939318302</v>
       </c>
       <c r="F22">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="G22" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C23" t="s">
         <v>33</v>
       </c>
       <c r="D23" t="s">
-        <v>10</v>
-      </c>
-      <c r="E23" s="1">
-        <v>15939318302</v>
+        <v>9</v>
+      </c>
+      <c r="E23">
+        <v>13721726762</v>
       </c>
       <c r="F23">
-        <v>5</v>
-      </c>
-      <c r="G23" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C24" t="s">
         <v>34</v>
       </c>
       <c r="D24" t="s">
-        <v>10</v>
-      </c>
-      <c r="E24">
-        <v>13721726762</v>
+        <v>9</v>
+      </c>
+      <c r="E24" s="1">
+        <v>13903935797</v>
       </c>
       <c r="F24">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="G24" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C25" t="s">
         <v>35</v>
       </c>
       <c r="D25" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E25" s="1">
-        <v>13903935797</v>
+        <v>15090218009</v>
       </c>
       <c r="F25">
-        <v>7</v>
-      </c>
-      <c r="G25" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="C26" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D26" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E26" s="1">
-        <v>15090218009</v>
+        <v>13623932898</v>
       </c>
       <c r="F26">
-        <v>8</v>
+        <v>1</v>
+      </c>
+      <c r="G26" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C27" t="s">
         <v>38</v>
       </c>
       <c r="D27" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E27" s="1">
-        <v>13623932898</v>
+        <v>15539339658</v>
       </c>
       <c r="F27">
-        <v>1</v>
-      </c>
-      <c r="G27" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C28" t="s">
         <v>39</v>
       </c>
       <c r="D28" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E28" s="1">
-        <v>15539339658</v>
+        <v>13193572112</v>
       </c>
       <c r="F28">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="G28" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C29" t="s">
         <v>40</v>
       </c>
       <c r="D29" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E29" s="1">
-        <v>13193572112</v>
+        <v>15518512212</v>
       </c>
       <c r="F29">
-        <v>3</v>
-      </c>
-      <c r="G29" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C30" t="s">
         <v>41</v>
       </c>
       <c r="D30" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E30" s="1">
-        <v>15518512212</v>
+        <v>13513943021</v>
       </c>
       <c r="F30">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="G30" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C31" t="s">
         <v>42</v>
       </c>
       <c r="D31" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E31" s="1">
-        <v>13513943021</v>
+        <v>13839283759</v>
       </c>
       <c r="F31">
-        <v>5</v>
-      </c>
-      <c r="G31" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C32" t="s">
         <v>43</v>
       </c>
       <c r="D32" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E32" s="1">
-        <v>13839283759</v>
+        <v>13781369836</v>
       </c>
       <c r="F32">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="G32" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C33" t="s">
         <v>44</v>
       </c>
       <c r="D33" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E33" s="1">
-        <v>13781369836</v>
+        <v>18238327212</v>
       </c>
       <c r="F33">
-        <v>7</v>
-      </c>
-      <c r="G33" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="C34" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D34" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E34" s="1">
-        <v>18238327212</v>
+        <v>18539330756</v>
       </c>
       <c r="F34">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C35" t="s">
         <v>47</v>
       </c>
       <c r="D35" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E35" s="1">
-        <v>18539330756</v>
+        <v>15839358163</v>
       </c>
       <c r="F35">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C36" t="s">
         <v>48</v>
       </c>
       <c r="D36" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E36" s="1">
-        <v>15839358163</v>
+        <v>15518522809</v>
       </c>
       <c r="F36">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="G36" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C37" t="s">
         <v>49</v>
       </c>
       <c r="D37" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E37" s="1">
-        <v>15518522809</v>
+        <v>15890496073</v>
       </c>
       <c r="F37">
-        <v>3</v>
-      </c>
-      <c r="G37" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C38" t="s">
         <v>50</v>
       </c>
       <c r="D38" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E38" s="1">
-        <v>15890496073</v>
+        <v>15639306288</v>
       </c>
       <c r="F38">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="G38" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C39" t="s">
         <v>51</v>
       </c>
       <c r="D39" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E39" s="1">
-        <v>15639306288</v>
+        <v>17339303182</v>
       </c>
       <c r="F39">
-        <v>5</v>
-      </c>
-      <c r="G39" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C40" t="s">
         <v>52</v>
       </c>
       <c r="D40" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E40" s="1">
-        <v>17339303182</v>
+        <v>15936786198</v>
       </c>
       <c r="F40">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="G40" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C41" t="s">
         <v>53</v>
       </c>
       <c r="D41" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E41" s="1">
-        <v>15936786198</v>
+        <v>13643938925</v>
       </c>
       <c r="F41">
-        <v>7</v>
-      </c>
-      <c r="G41" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="C42" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D42" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E42" s="1">
-        <v>13643938925</v>
+        <v>18639352711</v>
       </c>
       <c r="F42">
-        <v>8</v>
+        <v>1</v>
+      </c>
+      <c r="G42" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C43" t="s">
         <v>56</v>
       </c>
       <c r="D43" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E43" s="1">
-        <v>18639352711</v>
+        <v>13613932000</v>
       </c>
       <c r="F43">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G43" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C44" t="s">
         <v>57</v>
       </c>
       <c r="D44" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E44" s="1">
-        <v>13613932000</v>
+        <v>18639372028</v>
       </c>
       <c r="F44">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G44" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
-      <c r="A45">
-        <v>43</v>
-      </c>
-      <c r="B45" t="s">
-        <v>55</v>
-      </c>
-      <c r="C45" t="s">
-        <v>58</v>
-      </c>
-      <c r="D45" t="s">
-        <v>10</v>
-      </c>
-      <c r="E45" s="1">
-        <v>18639372028</v>
-      </c>
-      <c r="F45">
-        <v>5</v>
-      </c>
-      <c r="G45" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
